--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:12:52+00:00</t>
+    <t>2026-07-10T09:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T09:26:12+00:00</t>
+    <t>2026-07-20T12:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:02:06+00:00</t>
+    <t>2026-07-20T15:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -343,10 +343,10 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Custodian</t>
+  </si>
+  <si>
+    <t>Für Pflege und Aktualisierung des Versorgungsplans verantwortliche Stelle.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
+++ b/ci-build/StructureDefinition-onko-careplan-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
